--- a/2_Raw_Data/2_1_TPS/TPS_target_population_20260118.xlsx
+++ b/2_Raw_Data/2_1_TPS/TPS_target_population_20260118.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liuwe\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liuwe\Desktop\大团队科学样本代表性\BTS_Sample_Stage1_RR\BTS_Sample_Stage1_RR\2_Raw_Data\2_1_TPS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C1E03BB-6E2B-4E2C-AB08-7A9392580590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ECC1EF5-E523-4433-8C6C-7FC6695EDA2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="19392" windowHeight="11472" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4520,6 +4520,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4528,9 +4531,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4820,26 +4820,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="40"/>
-      <c r="D1" s="39" t="s">
+      <c r="A1" s="37"/>
+      <c r="D1" s="40" t="s">
         <v>686</v>
       </c>
-      <c r="E1" s="39"/>
-      <c r="F1" s="37" t="s">
+      <c r="E1" s="40"/>
+      <c r="F1" s="38" t="s">
         <v>687</v>
       </c>
-      <c r="G1" s="37"/>
-      <c r="H1" s="38" t="s">
+      <c r="G1" s="38"/>
+      <c r="H1" s="39" t="s">
         <v>688</v>
       </c>
-      <c r="I1" s="38"/>
-      <c r="J1" s="39" t="s">
+      <c r="I1" s="39"/>
+      <c r="J1" s="40" t="s">
         <v>689</v>
       </c>
-      <c r="K1" s="39"/>
+      <c r="K1" s="40"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="37" t="s">
         <v>1262</v>
       </c>
       <c r="B2" s="23" t="s">
